--- a/data/trans_dic/IP11-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses.</t>
+          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses. (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,29</t>
+          <t>2,57; 10,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 10,28</t>
+          <t>2,43; 10,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,05</t>
+          <t>2,1; 11,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,72</t>
+          <t>1,07; 7,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,46</t>
+          <t>1,44; 8,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 16,58</t>
+          <t>5,42; 16,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,69</t>
+          <t>0,71; 6,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,65</t>
+          <t>0,89; 5,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,07</t>
+          <t>2,82; 7,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,16</t>
+          <t>4,69; 11,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,7</t>
+          <t>1,9; 6,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,24</t>
+          <t>1,55; 5,4</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 12,31</t>
+          <t>3,06; 12,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,57</t>
+          <t>4,38; 14,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,4</t>
+          <t>0,58; 5,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,87</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,89</t>
+          <t>3,18; 12,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 15,34</t>
+          <t>5,77; 15,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,88</t>
+          <t>2,33; 9,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 13,39</t>
+          <t>3,4; 14,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,05; 10,11</t>
+          <t>4,0; 10,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 12,72</t>
+          <t>6,21; 13,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,99</t>
+          <t>2,02; 6,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,0</t>
+          <t>2,79; 9,14</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,19</t>
+          <t>2,02; 11,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 13,6</t>
+          <t>3,32; 13,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 7,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 14,83</t>
+          <t>4,77; 14,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 13,02</t>
+          <t>3,6; 12,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 14,16</t>
+          <t>3,61; 13,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 14,36</t>
+          <t>1,35; 13,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,82</t>
+          <t>4,59; 10,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 10,62</t>
+          <t>4,43; 11,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 8,37</t>
+          <t>2,31; 8,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 8,34</t>
+          <t>1,0; 8,1</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,2</t>
+          <t>4,09; 9,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,22</t>
+          <t>5,08; 11,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,86</t>
+          <t>2,05; 5,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,11</t>
+          <t>1,08; 4,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,58</t>
+          <t>4,62; 10,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 14,58</t>
+          <t>7,88; 15,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,61</t>
+          <t>3,71; 8,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,42</t>
+          <t>1,5; 6,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,98</t>
+          <t>5,0; 9,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,75</t>
+          <t>7,21; 11,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,46</t>
+          <t>3,3; 6,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,68</t>
+          <t>1,66; 4,7</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,22</t>
+          <t>0,77; 6,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,94</t>
+          <t>5,46; 13,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,24</t>
+          <t>2,35; 8,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,15</t>
+          <t>0,74; 4,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 13,66</t>
+          <t>5,24; 13,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 14,75</t>
+          <t>5,88; 14,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,79</t>
+          <t>3,31; 10,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,29</t>
+          <t>0,25; 3,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,97</t>
+          <t>4,09; 9,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,68; 12,25</t>
+          <t>6,66; 12,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,2</t>
+          <t>3,36; 8,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,15</t>
+          <t>0,72; 3,26</t>
         </is>
       </c>
     </row>
@@ -1416,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,19</t>
+          <t>1,01; 9,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 9,94</t>
+          <t>1,22; 11,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,47</t>
+          <t>0,96; 8,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,37 +1442,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,08; 20,06</t>
+          <t>7,08; 19,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,58; 15,64</t>
+          <t>3,34; 14,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,69</t>
+          <t>0,94; 5,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 13,63</t>
+          <t>5,57; 13,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,74</t>
+          <t>2,24; 8,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,75</t>
+          <t>0,67; 4,43</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,84</t>
+          <t>3,98; 6,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,05</t>
+          <t>5,98; 9,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,61</t>
+          <t>2,35; 4,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,72</t>
+          <t>1,75; 3,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,2</t>
+          <t>5,11; 8,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 11,94</t>
+          <t>8,19; 12,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,41</t>
+          <t>4,42; 7,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,67</t>
+          <t>2,14; 4,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,17</t>
+          <t>4,96; 7,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 9,98</t>
+          <t>7,56; 10,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,52</t>
+          <t>3,74; 5,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,78</t>
+          <t>2,21; 3,89</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses. (tasa de respuesta: 99,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5857</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4673</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4162</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3512</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8925</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3637</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9816</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13598</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>7148</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2683; 10505</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2190; 9566</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1731; 9719</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1114; 7793</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1404; 8144</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4861; 14528</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>707; 6325</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1214; 7912</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5696; 15438</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8432; 20035</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3446; 12117</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3746; 13040</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6039</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2533</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5628</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9428</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7213</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11667</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17132</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7968</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>9746</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2673; 10736</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4086; 13232</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>616; 5787</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2731; 10700</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5538; 15021</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2626; 10924</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3250; 13543</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6939; 18169</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>11762; 24777</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4405; 13183</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5304; 17389</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3778</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3657</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12306</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6384</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4392</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1362; 7620</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2862; 11446</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2885</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3948</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4741; 14501</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3128; 11170</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2719; 10027</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>864; 8794</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>7654; 18268</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7660; 19481</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3175; 11775</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1153; 9375</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12716</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15854</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8038</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5320</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14533</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>24256</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12332</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7151</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>27249</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>40110</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>20371</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>12471</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>8216; 19262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10455; 23185</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4563; 13284</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2366; 10800</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>9332; 22091</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>17851; 34372</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7825; 18720</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3254; 14043</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20123; 37297</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>31169; 50781</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>14273; 28319</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>7220; 20462</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13260</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6590</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2676</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11190</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13538</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8835</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>14046</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>26798</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15425</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>801; 7163</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8147; 19682</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3194; 11627</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>880; 5802</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6668; 16887</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8291; 20238</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4738; 14583</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>401; 6019</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>9463; 21463</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>19333; 36521</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>9396; 22707</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2040; 9182</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2840</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>9230</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>4077</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>11273</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5793</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2925</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>757; 6998</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>656; 6062</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3158</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>658; 5729</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4342</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>5240; 14464</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2242; 9732</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3131</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1378; 7567</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>7122; 16955</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2871; 10914</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>948; 6237</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>34085</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>49767</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>22123</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45163</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>71450</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>24034</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>79249</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>121217</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>62847</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>41185</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>25414; 43741</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>40547; 61589</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>15754; 30931</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>11506; 26207</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>34968; 56384</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>58505; 86002</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>31314; 52609</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>16003; 34233</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>65597; 93266</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>105304; 139868</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>51541; 76831</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>31099; 54740</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 10,07</t>
+          <t>2,73; 10,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 10,64</t>
+          <t>2,22; 10,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,81</t>
+          <t>2,12; 10,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,46</t>
+          <t>1,17; 7,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,35</t>
+          <t>1,39; 7,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 16,18</t>
+          <t>5,44; 16,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,38</t>
+          <t>0,71; 7,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,78</t>
+          <t>0,74; 6,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,65</t>
+          <t>2,85; 7,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,15</t>
+          <t>4,67; 11,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,68</t>
+          <t>1,99; 6,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,4</t>
+          <t>1,45; 5,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 12,29</t>
+          <t>3,22; 12,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 14,19</t>
+          <t>4,14; 13,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,47</t>
+          <t>0,58; 5,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,77; 7,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 12,45</t>
+          <t>3,34; 12,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,64</t>
+          <t>5,68; 15,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,69</t>
+          <t>2,57; 9,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 14,17</t>
+          <t>3,42; 13,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,48</t>
+          <t>4,33; 10,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 13,09</t>
+          <t>6,3; 12,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,03</t>
+          <t>2,08; 6,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,14</t>
+          <t>2,69; 9,47</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,31</t>
+          <t>1,99; 12,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 13,28</t>
+          <t>3,27; 12,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 5,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,61</t>
+          <t>0,0; 7,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 14,6</t>
+          <t>5,13; 13,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 12,86</t>
+          <t>3,31; 12,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 13,29</t>
+          <t>3,65; 13,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,77</t>
+          <t>1,44; 14,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,96</t>
+          <t>4,54; 10,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,26</t>
+          <t>4,17; 10,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,58</t>
+          <t>2,15; 8,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,1</t>
+          <t>1,39; 8,03</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,6</t>
+          <t>3,76; 9,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,27</t>
+          <t>4,89; 10,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,98</t>
+          <t>1,93; 5,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,94</t>
+          <t>0,95; 4,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,93</t>
+          <t>4,53; 10,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 15,18</t>
+          <t>7,75; 14,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 8,88</t>
+          <t>3,59; 9,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,47</t>
+          <t>1,35; 6,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,26</t>
+          <t>4,96; 9,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,75</t>
+          <t>7,2; 11,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,54</t>
+          <t>3,28; 6,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,7</t>
+          <t>1,58; 4,61</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,88</t>
+          <t>0,69; 6,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 13,19</t>
+          <t>5,58; 13,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,54</t>
+          <t>2,51; 8,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,86</t>
+          <t>0,74; 5,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,27</t>
+          <t>5,43; 13,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 14,35</t>
+          <t>6,35; 15,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,19</t>
+          <t>3,26; 10,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,7</t>
+          <t>0,26; 3,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,27</t>
+          <t>3,9; 9,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 12,58</t>
+          <t>6,45; 12,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,13</t>
+          <t>3,58; 8,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,26</t>
+          <t>0,69; 3,14</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,35</t>
+          <t>0,95; 9,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,24</t>
+          <t>1,24; 10,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,32</t>
+          <t>0,94; 8,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,0</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,08; 19,54</t>
+          <t>7,3; 19,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,34; 14,49</t>
+          <t>3,32; 14,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,35</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,14</t>
+          <t>0,96; 5,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,57; 13,25</t>
+          <t>5,4; 13,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,51</t>
+          <t>2,09; 8,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,43</t>
+          <t>0,67; 4,6</t>
         </is>
       </c>
     </row>
@@ -1562,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 9,08</t>
+          <t>5,78; 9,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,62</t>
+          <t>2,27; 4,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,98</t>
+          <t>1,75; 3,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 8,24</t>
+          <t>5,25; 8,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,04</t>
+          <t>8,38; 12,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 7,43</t>
+          <t>4,42; 7,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,58</t>
+          <t>2,17; 4,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,05</t>
+          <t>5,01; 7,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,05</t>
+          <t>7,59; 10,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,58</t>
+          <t>3,7; 5,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,89</t>
+          <t>2,17; 3,84</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2683; 10505</t>
+          <t>2846; 10697</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2190; 9566</t>
+          <t>1997; 9324</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1731; 9719</t>
+          <t>1746; 8697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1114; 7793</t>
+          <t>1225; 7900</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1404; 8144</t>
+          <t>1361; 7555</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4861; 14528</t>
+          <t>4879; 14637</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>707; 6325</t>
+          <t>708; 7001</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1214; 7912</t>
+          <t>1009; 8459</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5696; 15438</t>
+          <t>5758; 15643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8432; 20035</t>
+          <t>8395; 20409</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3446; 12117</t>
+          <t>3618; 12275</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3746; 13040</t>
+          <t>3509; 12813</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2673; 10736</t>
+          <t>2816; 10792</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4086; 13232</t>
+          <t>3862; 12449</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>616; 5787</t>
+          <t>610; 5562</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6674</t>
+          <t>727; 7124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2731; 10700</t>
+          <t>2870; 10345</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5538; 15021</t>
+          <t>5451; 15234</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2626; 10924</t>
+          <t>2899; 10542</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3250; 13543</t>
+          <t>3266; 13318</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6939; 18169</t>
+          <t>7511; 18725</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11762; 24777</t>
+          <t>11932; 24166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4405; 13183</t>
+          <t>4553; 13713</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5304; 17389</t>
+          <t>5125; 18018</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1362; 7620</t>
+          <t>1344; 8390</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2862; 11446</t>
+          <t>2814; 11061</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2885</t>
+          <t>0; 3561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3948</t>
+          <t>0; 4094</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4741; 14501</t>
+          <t>5101; 13826</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3128; 11170</t>
+          <t>2879; 11142</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2719; 10027</t>
+          <t>2752; 10183</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>864; 8794</t>
+          <t>917; 9032</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7654; 18268</t>
+          <t>7562; 17787</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7660; 19481</t>
+          <t>7220; 18597</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3175; 11775</t>
+          <t>2953; 11529</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1153; 9375</t>
+          <t>1613; 9287</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8216; 19262</t>
+          <t>7547; 18929</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10455; 23185</t>
+          <t>10059; 22451</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4563; 13284</t>
+          <t>4293; 13296</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2366; 10800</t>
+          <t>2063; 10489</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9332; 22091</t>
+          <t>9150; 21809</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17851; 34372</t>
+          <t>17547; 32951</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7825; 18720</t>
+          <t>7573; 19312</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3254; 14043</t>
+          <t>2942; 14420</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20123; 37297</t>
+          <t>19965; 36278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31169; 50781</t>
+          <t>31110; 51078</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14273; 28319</t>
+          <t>14194; 28663</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7220; 20462</t>
+          <t>6882; 20063</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>801; 7163</t>
+          <t>714; 6861</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8147; 19682</t>
+          <t>8328; 20518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3194; 11627</t>
+          <t>3412; 11706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>880; 5802</t>
+          <t>880; 6175</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6668; 16887</t>
+          <t>6910; 17057</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8291; 20238</t>
+          <t>8953; 21169</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4738; 14583</t>
+          <t>4661; 15313</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>401; 6019</t>
+          <t>418; 5918</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9463; 21463</t>
+          <t>9021; 20846</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19333; 36521</t>
+          <t>18728; 34907</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9396; 22707</t>
+          <t>10011; 23115</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2040; 9182</t>
+          <t>1954; 8849</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>757; 6998</t>
+          <t>710; 6828</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>656; 6062</t>
+          <t>671; 5418</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3158</t>
+          <t>0; 3024</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>658; 5729</t>
+          <t>648; 5880</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4342</t>
+          <t>0; 4334</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5240; 14464</t>
+          <t>5403; 14786</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2242; 9732</t>
+          <t>2232; 9968</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3131</t>
+          <t>0; 3032</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1378; 7567</t>
+          <t>1416; 8656</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7122; 16955</t>
+          <t>6912; 17089</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2871; 10914</t>
+          <t>2676; 11159</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>948; 6237</t>
+          <t>939; 6486</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25414; 43741</t>
+          <t>25402; 43793</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40547; 61589</t>
+          <t>39202; 62381</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15754; 30931</t>
+          <t>15220; 30626</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11506; 26207</t>
+          <t>11512; 25681</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34968; 56384</t>
+          <t>35919; 55404</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58505; 86002</t>
+          <t>59831; 86218</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31314; 52609</t>
+          <t>31328; 51939</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16003; 34233</t>
+          <t>16242; 34453</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>65597; 93266</t>
+          <t>66341; 94067</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>105304; 139868</t>
+          <t>105618; 140406</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51541; 76831</t>
+          <t>50906; 76493</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>31099; 54740</t>
+          <t>30504; 53969</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,61%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,06%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 10,25</t>
+          <t>1,43; 8,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 10,37</t>
+          <t>5,5; 16,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 10,57</t>
+          <t>0,67; 6,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,56</t>
+          <t>0,86; 6,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,75</t>
+          <t>2,65; 10,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 16,31</t>
+          <t>2,24; 10,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,06</t>
+          <t>2,0; 11,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,18</t>
+          <t>1,34; 8,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,75</t>
+          <t>2,8; 8,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 11,36</t>
+          <t>4,91; 11,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,77</t>
+          <t>1,95; 6,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,31</t>
+          <t>1,31; 5,41</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,91%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,95%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 12,35</t>
+          <t>3,18; 11,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 13,35</t>
+          <t>5,74; 15,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,26</t>
+          <t>2,27; 9,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,52</t>
+          <t>3,27; 13,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 12,03</t>
+          <t>3,69; 12,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 15,86</t>
+          <t>4,53; 14,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,35</t>
+          <t>0,57; 5,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 13,93</t>
+          <t>0,68; 6,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 10,8</t>
+          <t>4,05; 10,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,77</t>
+          <t>6,0; 12,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,28</t>
+          <t>1,88; 5,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,47</t>
+          <t>2,58; 8,64</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,61%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,23%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,67%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 12,45</t>
+          <t>5,07; 14,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 12,84</t>
+          <t>3,2; 13,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,76</t>
+          <t>3,75; 14,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,89</t>
+          <t>1,68; 15,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 13,92</t>
+          <t>2,51; 11,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 12,82</t>
+          <t>3,82; 13,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 13,5</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 14,14</t>
+          <t>0,0; 8,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,67</t>
+          <t>4,41; 10,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 10,75</t>
+          <t>4,34; 10,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 8,4</t>
+          <t>2,15; 8,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,03</t>
+          <t>1,46; 8,51</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,33%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,71%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 9,43</t>
+          <t>4,7; 10,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,91</t>
+          <t>7,68; 14,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,99</t>
+          <t>3,56; 8,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,82</t>
+          <t>1,46; 6,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,79</t>
+          <t>3,96; 9,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 14,55</t>
+          <t>4,91; 11,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,16</t>
+          <t>1,93; 5,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,64</t>
+          <t>1,37; 5,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,01</t>
+          <t>4,84; 8,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 11,82</t>
+          <t>7,13; 11,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,62</t>
+          <t>3,31; 6,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,61</t>
+          <t>1,81; 4,88</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,89%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>4,84%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,59</t>
+          <t>5,38; 13,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 13,75</t>
+          <t>6,14; 14,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,59</t>
+          <t>3,42; 10,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,17</t>
+          <t>0,2; 3,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 13,4</t>
+          <t>0,69; 6,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 15,01</t>
+          <t>5,75; 12,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 10,7</t>
+          <t>2,31; 8,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,64</t>
+          <t>0,84; 5,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,01</t>
+          <t>3,87; 8,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,03</t>
+          <t>6,68; 12,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,28</t>
+          <t>3,48; 8,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,14</t>
+          <t>0,72; 3,31</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3,79%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3,79%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,12</t>
+          <t>0,0; 6,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,05</t>
+          <t>7,08; 20,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>3,58; 15,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,54</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,92; 9,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,3; 19,97</t>
+          <t>1,23; 9,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 14,84</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>1,04; 9,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,88</t>
+          <t>0,98; 5,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,4; 13,36</t>
+          <t>5,17; 13,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,7</t>
+          <t>1,81; 8,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,6</t>
+          <t>0,88; 4,96</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5,34%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3,31%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,85</t>
+          <t>5,25; 8,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,2</t>
+          <t>8,38; 11,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,58</t>
+          <t>4,53; 7,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,91</t>
+          <t>2,19; 4,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,09</t>
+          <t>3,95; 6,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 12,07</t>
+          <t>5,85; 9,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 7,33</t>
+          <t>2,35; 4,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,61</t>
+          <t>1,82; 4,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 7,11</t>
+          <t>5,04; 7,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 10,08</t>
+          <t>7,51; 9,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 5,55</t>
+          <t>3,65; 5,52</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,84</t>
+          <t>2,31; 3,97</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,37 +1791,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8925</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3355</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5857</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4673</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4162</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3512</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8925</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6837</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2846; 10697</t>
+          <t>1391; 8257</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1997; 9324</t>
+          <t>4939; 14882</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1746; 8697</t>
+          <t>665; 6633</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1225; 7900</t>
+          <t>1057; 7429</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1361; 7555</t>
+          <t>2765; 10739</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4879; 14637</t>
+          <t>2018; 9244</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>708; 7001</t>
+          <t>1644; 9094</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1009; 8459</t>
+          <t>1384; 8232</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5758; 15643</t>
+          <t>5651; 16303</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8395; 20409</t>
+          <t>8826; 20047</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3618; 12275</t>
+          <t>3538; 12163</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3509; 12813</t>
+          <t>2964; 12191</t>
         </is>
       </c>
     </row>
@@ -2004,37 +2004,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5628</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9428</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6039</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7704</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2065</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2533</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5628</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9428</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9287</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2816; 10792</t>
+          <t>2731; 10219</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3862; 12449</t>
+          <t>5509; 14733</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>610; 5562</t>
+          <t>2559; 11141</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>727; 7124</t>
+          <t>2992; 12221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2870; 10345</t>
+          <t>3229; 10755</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5451; 15234</t>
+          <t>4225; 13589</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2899; 10542</t>
+          <t>607; 5705</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3266; 13318</t>
+          <t>654; 6607</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7511; 18725</t>
+          <t>7017; 17526</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11932; 24166</t>
+          <t>11356; 24082</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4553; 13713</t>
+          <t>4113; 13078</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5125; 18018</t>
+          <t>4840; 16232</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3778</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6232</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>696</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6074</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5688</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>766</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4316</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1344; 8390</t>
+          <t>5036; 14731</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2814; 11061</t>
+          <t>2784; 11310</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3561</t>
+          <t>2828; 10683</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4094</t>
+          <t>957; 8729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5101; 13826</t>
+          <t>1692; 7543</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2879; 11142</t>
+          <t>3292; 11713</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2752; 10183</t>
+          <t>0; 3783</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>917; 9032</t>
+          <t>0; 4699</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7562; 17787</t>
+          <t>7359; 18039</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7220; 18597</t>
+          <t>7509; 18378</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2953; 11529</t>
+          <t>2956; 11493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1613; 9287</t>
+          <t>1607; 9393</t>
         </is>
       </c>
     </row>
@@ -2415,37 +2415,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14533</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24256</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12332</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6389</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>12716</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15854</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8038</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5320</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14533</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24256</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12332</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>11593</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7547; 18929</t>
+          <t>9490; 21376</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10059; 22451</t>
+          <t>17388; 33020</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4293; 13296</t>
+          <t>7504; 18147</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2063; 10489</t>
+          <t>2939; 12175</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9150; 21809</t>
+          <t>7958; 18470</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17547; 32951</t>
+          <t>10102; 23070</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7573; 19312</t>
+          <t>4277; 13002</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2942; 14420</t>
+          <t>2442; 10091</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19965; 36278</t>
+          <t>19508; 36173</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31110; 51078</t>
+          <t>30826; 50759</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14194; 28663</t>
+          <t>14312; 27963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6882; 20063</t>
+          <t>6884; 18530</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11190</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13538</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8835</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2856</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>13260</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>6590</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2676</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>11190</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13538</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8835</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4369</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>714; 6861</t>
+          <t>6854; 17393</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8328; 20518</t>
+          <t>8660; 20810</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3412; 11706</t>
+          <t>4901; 15436</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>880; 6175</t>
+          <t>292; 5529</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6910; 17057</t>
+          <t>720; 6479</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8953; 21169</t>
+          <t>8574; 19310</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4661; 15313</t>
+          <t>3140; 11224</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>418; 5918</t>
+          <t>999; 6018</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9021; 20846</t>
+          <t>8959; 20754</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18728; 34907</t>
+          <t>19399; 35553</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10011; 23115</t>
+          <t>9709; 22890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1954; 8849</t>
+          <t>1918; 8828</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9230</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2840</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>573</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9230</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5220</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3032</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>710; 6828</t>
+          <t>0; 4343</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>671; 5418</t>
+          <t>5245; 14856</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3024</t>
+          <t>2403; 10503</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>648; 5880</t>
+          <t>0; 2367</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4334</t>
+          <t>686; 6882</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5403; 14786</t>
+          <t>663; 5359</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2232; 9968</t>
+          <t>0; 2882</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3032</t>
+          <t>734; 6377</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1416; 8656</t>
+          <t>1438; 8385</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6912; 17089</t>
+          <t>6617; 17439</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2676; 11159</t>
+          <t>2326; 11212</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>939; 6486</t>
+          <t>1216; 6878</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>45163</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>71450</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>34085</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>49767</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>22123</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>45163</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>71450</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25402; 43793</t>
+          <t>35967; 56167</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39202; 62381</t>
+          <t>59820; 85265</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15220; 30626</t>
+          <t>32079; 52484</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11512; 25681</t>
+          <t>15053; 32584</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35919; 55404</t>
+          <t>25219; 43719</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59831; 86218</t>
+          <t>39670; 61375</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31328; 51939</t>
+          <t>15729; 30874</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16242; 34453</t>
+          <t>11319; 25202</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66341; 94067</t>
+          <t>66757; 94888</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>105618; 140406</t>
+          <t>104618; 138902</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50906; 76493</t>
+          <t>50253; 76070</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30504; 53969</t>
+          <t>30259; 51941</t>
         </is>
       </c>
     </row>
